--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1190"/>
+  <dimension ref="A1:I1195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -39681,8 +39681,13 @@
           <t>Calgary Hitmen</t>
         </is>
       </c>
-      <c r="F1188" t="n">
-        <v/>
+      <c r="F1188" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="G1188" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1189">
@@ -39709,8 +39714,13 @@
           <t>Seattle Thunderbirds</t>
         </is>
       </c>
-      <c r="F1189" t="n">
-        <v/>
+      <c r="F1189" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="G1189" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1190">
@@ -39737,7 +39747,152 @@
           <t>Everett Silvertips</t>
         </is>
       </c>
-      <c r="F1190" t="n">
+      <c r="F1190" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="G1190" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="n">
+        <v>1022774</v>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>Tue, Feb 24, 2026</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="E1191" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="F1191" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="n">
+        <v>1022773</v>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>Tue, Feb 24, 2026</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="E1192" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="F1192" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="n">
+        <v>1022776</v>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>Tue, Feb 24, 2026</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="E1193" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="F1193" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="n">
+        <v>1022775</v>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>Tue, Feb 24, 2026</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="E1194" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="F1194" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="n">
+        <v>1022777</v>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>Tue, Feb 24, 2026</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="E1195" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="F1195" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1195"/>
+  <dimension ref="A1:I1200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -39780,8 +39780,13 @@
           <t>Calgary Hitmen</t>
         </is>
       </c>
-      <c r="F1191" t="n">
-        <v/>
+      <c r="F1191" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="G1191" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1192">
@@ -39808,8 +39813,13 @@
           <t>Prince George Cougars</t>
         </is>
       </c>
-      <c r="F1192" t="n">
-        <v/>
+      <c r="F1192" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="G1192" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1193">
@@ -39836,8 +39846,13 @@
           <t>Penticton Vees</t>
         </is>
       </c>
-      <c r="F1193" t="n">
-        <v/>
+      <c r="F1193" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="G1193" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1194">
@@ -39864,8 +39879,13 @@
           <t>Medicine Hat Tigers</t>
         </is>
       </c>
-      <c r="F1194" t="n">
-        <v/>
+      <c r="F1194" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="G1194" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1195">
@@ -39892,7 +39912,152 @@
           <t>Victoria Royals</t>
         </is>
       </c>
-      <c r="F1195" t="n">
+      <c r="F1195" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="G1195" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="n">
+        <v>1022780</v>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>Wed, Feb 25, 2026</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="D1196" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="E1196" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="F1196" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="n">
+        <v>1022781</v>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>Wed, Feb 25, 2026</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="E1197" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="F1197" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="n">
+        <v>1022779</v>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>Wed, Feb 25, 2026</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="E1198" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="F1198" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="n">
+        <v>1022778</v>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>Wed, Feb 25, 2026</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="E1199" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="F1199" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="n">
+        <v>1022782</v>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>Wed, Feb 25, 2026</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="E1200" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="F1200" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1200"/>
+  <dimension ref="A1:I1211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -39945,8 +39945,13 @@
           <t>Prince George Cougars</t>
         </is>
       </c>
-      <c r="F1196" t="n">
-        <v/>
+      <c r="F1196" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="G1196" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1197">
@@ -39973,8 +39978,13 @@
           <t>Saskatoon Blades</t>
         </is>
       </c>
-      <c r="F1197" t="n">
-        <v/>
+      <c r="F1197" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="G1197" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1198">
@@ -40001,8 +40011,13 @@
           <t>Lethbridge Hurricanes</t>
         </is>
       </c>
-      <c r="F1198" t="n">
-        <v/>
+      <c r="F1198" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="G1198" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1199">
@@ -40029,8 +40044,13 @@
           <t>Kelowna Rockets</t>
         </is>
       </c>
-      <c r="F1199" t="n">
-        <v/>
+      <c r="F1199" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="G1199" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1200">
@@ -40057,7 +40077,320 @@
           <t>Spokane Chiefs</t>
         </is>
       </c>
-      <c r="F1200" t="n">
+      <c r="F1200" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="G1200" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="n">
+        <v>1022783</v>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>Fri, Feb 27, 2026</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="E1201" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="F1201" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="n">
+        <v>1022788</v>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>Fri, Feb 27, 2026</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="E1202" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1202" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="n">
+        <v>1022790</v>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>Fri, Feb 27, 2026</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="E1203" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="F1203" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="n">
+        <v>1022784</v>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>Fri, Feb 27, 2026</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="E1204" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="F1204" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="n">
+        <v>1022787</v>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>Fri, Feb 27, 2026</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="E1205" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="F1205" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="n">
+        <v>1022789</v>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>Fri, Feb 27, 2026</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="E1206" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="F1206" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="n">
+        <v>1022792</v>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>Fri, Feb 27, 2026</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="E1207" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="F1207" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="n">
+        <v>1022785</v>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>Fri, Feb 27, 2026</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="E1208" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="F1208" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="n">
+        <v>1022786</v>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>Fri, Feb 27, 2026</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="E1209" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="F1209" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="n">
+        <v>1022791</v>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>Fri, Feb 27, 2026</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="E1210" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="F1210" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="n">
+        <v>1022793</v>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>Fri, Feb 27, 2026</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="E1211" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="F1211" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1211"/>
+  <dimension ref="A1:I1222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -40110,8 +40110,13 @@
           <t>Regina Pats</t>
         </is>
       </c>
-      <c r="F1201" t="n">
-        <v/>
+      <c r="F1201" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="G1201" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1202">
@@ -40138,8 +40143,13 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1202" t="n">
-        <v/>
+      <c r="F1202" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="G1202" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1203">
@@ -40166,8 +40176,13 @@
           <t>Prince George Cougars</t>
         </is>
       </c>
-      <c r="F1203" t="n">
-        <v/>
+      <c r="F1203" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="G1203" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1204">
@@ -40194,8 +40209,13 @@
           <t>Medicine Hat Tigers</t>
         </is>
       </c>
-      <c r="F1204" t="n">
-        <v/>
+      <c r="F1204" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="G1204" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1205">
@@ -40222,8 +40242,13 @@
           <t>Lethbridge Hurricanes</t>
         </is>
       </c>
-      <c r="F1205" t="n">
-        <v/>
+      <c r="F1205" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="G1205" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1206">
@@ -40250,8 +40275,13 @@
           <t>Edmonton Oil Kings</t>
         </is>
       </c>
-      <c r="F1206" t="n">
-        <v/>
+      <c r="F1206" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="G1206" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1207">
@@ -40278,8 +40308,13 @@
           <t>Seattle Thunderbirds</t>
         </is>
       </c>
-      <c r="F1207" t="n">
-        <v/>
+      <c r="F1207" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="G1207" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1208">
@@ -40306,8 +40341,13 @@
           <t>Everett Silvertips</t>
         </is>
       </c>
-      <c r="F1208" t="n">
-        <v/>
+      <c r="F1208" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="G1208" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1209">
@@ -40334,8 +40374,13 @@
           <t>Kelowna Rockets</t>
         </is>
       </c>
-      <c r="F1209" t="n">
-        <v/>
+      <c r="F1209" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="G1209" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1210">
@@ -40362,8 +40407,13 @@
           <t>Spokane Chiefs</t>
         </is>
       </c>
-      <c r="F1210" t="n">
-        <v/>
+      <c r="F1210" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="G1210" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1211">
@@ -40390,7 +40440,320 @@
           <t>Portland Winterhawks</t>
         </is>
       </c>
-      <c r="F1211" t="n">
+      <c r="F1211" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="G1211" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="n">
+        <v>1022797</v>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>Sat, Feb 28, 2026</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="E1212" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="F1212" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="n">
+        <v>1022800</v>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>Sat, Feb 28, 2026</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="E1213" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="F1213" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="n">
+        <v>1022803</v>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>Sat, Feb 28, 2026</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="E1214" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="F1214" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="n">
+        <v>1022798</v>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>Sat, Feb 28, 2026</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="E1215" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1215" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="n">
+        <v>1022799</v>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>Sat, Feb 28, 2026</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="E1216" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="F1216" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="n">
+        <v>1022794</v>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>Sat, Feb 28, 2026</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="E1217" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="F1217" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="n">
+        <v>1022795</v>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>Sat, Feb 28, 2026</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="E1218" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="F1218" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="n">
+        <v>1022796</v>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>Sat, Feb 28, 2026</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="E1219" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="F1219" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="n">
+        <v>1022804</v>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>Sat, Feb 28, 2026</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="E1220" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="F1220" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="n">
+        <v>1022801</v>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>Sat, Feb 28, 2026</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="E1221" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="F1221" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="n">
+        <v>1022802</v>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>Sat, Feb 28, 2026</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="E1222" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="F1222" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1222"/>
+  <dimension ref="A1:I1224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -40473,8 +40473,13 @@
           <t>Penticton Vees</t>
         </is>
       </c>
-      <c r="F1212" t="n">
-        <v/>
+      <c r="F1212" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="G1212" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1213">
@@ -40501,8 +40506,13 @@
           <t>Saskatoon Blades</t>
         </is>
       </c>
-      <c r="F1213" t="n">
-        <v/>
+      <c r="F1213" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="G1213" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1214">
@@ -40529,8 +40539,13 @@
           <t>Portland Winterhawks</t>
         </is>
       </c>
-      <c r="F1214" t="n">
-        <v/>
+      <c r="F1214" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="G1214" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1215">
@@ -40557,8 +40572,13 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1215" t="n">
-        <v/>
+      <c r="F1215" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="G1215" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1216">
@@ -40585,8 +40605,13 @@
           <t>Red Deer Rebels</t>
         </is>
       </c>
-      <c r="F1216" t="n">
-        <v/>
+      <c r="F1216" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="G1216" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1217">
@@ -40613,8 +40638,13 @@
           <t>Edmonton Oil Kings</t>
         </is>
       </c>
-      <c r="F1217" t="n">
-        <v/>
+      <c r="F1217" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="G1217" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1218">
@@ -40641,8 +40671,13 @@
           <t>Kamloops Blazers</t>
         </is>
       </c>
-      <c r="F1218" t="n">
-        <v/>
+      <c r="F1218" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="G1218" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1219">
@@ -40669,8 +40704,13 @@
           <t>Medicine Hat Tigers</t>
         </is>
       </c>
-      <c r="F1219" t="n">
-        <v/>
+      <c r="F1219" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="G1219" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1220">
@@ -40697,8 +40737,13 @@
           <t>Kelowna Rockets</t>
         </is>
       </c>
-      <c r="F1220" t="n">
-        <v/>
+      <c r="F1220" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="G1220" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1221">
@@ -40725,8 +40770,13 @@
           <t>Everett Silvertips</t>
         </is>
       </c>
-      <c r="F1221" t="n">
-        <v/>
+      <c r="F1221" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="G1221" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1222">
@@ -40753,7 +40803,68 @@
           <t>Spokane Chiefs</t>
         </is>
       </c>
-      <c r="F1222" t="n">
+      <c r="F1222" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="G1222" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="n">
+        <v>1022805</v>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>Sun, Mar 1, 2026</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="E1223" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="F1223" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="n">
+        <v>1022806</v>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>Sun, Mar 1, 2026</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="E1224" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="F1224" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1224"/>
+  <dimension ref="A1:I1229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -40836,8 +40836,13 @@
           <t>Edmonton Oil Kings</t>
         </is>
       </c>
-      <c r="F1223" t="n">
-        <v/>
+      <c r="F1223" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="G1223" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1224">
@@ -40864,7 +40869,152 @@
           <t>Everett Silvertips</t>
         </is>
       </c>
-      <c r="F1224" t="n">
+      <c r="F1224" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="G1224" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="n">
+        <v>1022808</v>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>Tue, Mar 3, 2026</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="D1225" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="E1225" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="F1225" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="n">
+        <v>1022809</v>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>Tue, Mar 3, 2026</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="D1226" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="E1226" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1226" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="n">
+        <v>1022810</v>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>Tue, Mar 3, 2026</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="D1227" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="E1227" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="F1227" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="n">
+        <v>1022807</v>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>Tue, Mar 3, 2026</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="D1228" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="E1228" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="F1228" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="n">
+        <v>1022811</v>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>Tue, Mar 3, 2026</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="D1229" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="E1229" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="F1229" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1229"/>
+  <dimension ref="A1:I1233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -40902,8 +40902,13 @@
           <t>Calgary Hitmen</t>
         </is>
       </c>
-      <c r="F1225" t="n">
-        <v/>
+      <c r="F1225" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="G1225" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1226">
@@ -40930,8 +40935,13 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1226" t="n">
-        <v/>
+      <c r="F1226" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="G1226" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1227">
@@ -40958,8 +40968,13 @@
           <t>Medicine Hat Tigers</t>
         </is>
       </c>
-      <c r="F1227" t="n">
-        <v/>
+      <c r="F1227" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="G1227" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1228">
@@ -40986,8 +41001,13 @@
           <t>Seattle Thunderbirds</t>
         </is>
       </c>
-      <c r="F1228" t="n">
-        <v/>
+      <c r="F1228" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="G1228" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1229">
@@ -41014,7 +41034,124 @@
           <t>Vancouver Giants</t>
         </is>
       </c>
-      <c r="F1229" t="n">
+      <c r="F1229" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="G1229" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="n">
+        <v>1022812</v>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>Wed, Mar 4, 2026</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="D1230" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="E1230" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="F1230" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="n">
+        <v>1022814</v>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>Wed, Mar 4, 2026</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="D1231" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="E1231" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="F1231" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="n">
+        <v>1022815</v>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>Wed, Mar 4, 2026</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="D1232" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="E1232" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="F1232" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="n">
+        <v>1022813</v>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>Wed, Mar 4, 2026</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="D1233" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="E1233" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="F1233" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1233"/>
+  <dimension ref="A1:I1244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -41067,8 +41067,13 @@
           <t>Medicine Hat Tigers</t>
         </is>
       </c>
-      <c r="F1230" t="n">
-        <v/>
+      <c r="F1230" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="G1230" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1231">
@@ -41095,8 +41100,13 @@
           <t>Saskatoon Blades</t>
         </is>
       </c>
-      <c r="F1231" t="n">
-        <v/>
+      <c r="F1231" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="G1231" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1232">
@@ -41123,8 +41133,13 @@
           <t>Calgary Hitmen</t>
         </is>
       </c>
-      <c r="F1232" t="n">
-        <v/>
+      <c r="F1232" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="G1232" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1233">
@@ -41151,7 +41166,320 @@
           <t>Spokane Chiefs</t>
         </is>
       </c>
-      <c r="F1233" t="n">
+      <c r="F1233" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="G1233" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="n">
+        <v>1022823</v>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>Fri, Mar 6, 2026</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="E1234" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="F1234" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="n">
+        <v>1022824</v>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>Fri, Mar 6, 2026</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="D1235" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="E1235" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="F1235" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="n">
+        <v>1022825</v>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>Fri, Mar 6, 2026</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="D1236" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="E1236" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="F1236" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="n">
+        <v>1022816</v>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>Fri, Mar 6, 2026</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="D1237" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="E1237" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1237" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="n">
+        <v>1022820</v>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>Fri, Mar 6, 2026</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="D1238" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="E1238" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="F1238" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="n">
+        <v>1022818</v>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>Fri, Mar 6, 2026</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="D1239" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="E1239" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="F1239" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="n">
+        <v>1022822</v>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>Fri, Mar 6, 2026</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="D1240" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="E1240" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="F1240" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="n">
+        <v>1022817</v>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>Fri, Mar 6, 2026</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="D1241" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="E1241" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="F1241" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="n">
+        <v>1022819</v>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>Fri, Mar 6, 2026</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="D1242" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="E1242" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="F1242" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="n">
+        <v>1022821</v>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>Fri, Mar 6, 2026</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="D1243" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="E1243" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="F1243" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="n">
+        <v>1022826</v>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>Fri, Mar 6, 2026</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="D1244" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="E1244" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="F1244" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1244"/>
+  <dimension ref="A1:I1254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -41199,8 +41199,13 @@
           <t>Regina Pats</t>
         </is>
       </c>
-      <c r="F1234" t="n">
-        <v/>
+      <c r="F1234" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="G1234" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1235">
@@ -41227,8 +41232,13 @@
           <t>Saskatoon Blades</t>
         </is>
       </c>
-      <c r="F1235" t="n">
-        <v/>
+      <c r="F1235" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="G1235" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1236">
@@ -41255,8 +41265,13 @@
           <t>Brandon Wheat Kings</t>
         </is>
       </c>
-      <c r="F1236" t="n">
-        <v/>
+      <c r="F1236" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="G1236" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1237">
@@ -41283,8 +41298,13 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1237" t="n">
-        <v/>
+      <c r="F1237" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="G1237" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1238">
@@ -41311,8 +41331,13 @@
           <t>Medicine Hat Tigers</t>
         </is>
       </c>
-      <c r="F1238" t="n">
-        <v/>
+      <c r="F1238" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="G1238" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1239">
@@ -41339,8 +41364,13 @@
           <t>Victoria Royals</t>
         </is>
       </c>
-      <c r="F1239" t="n">
-        <v/>
+      <c r="F1239" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="G1239" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1240">
@@ -41367,8 +41397,13 @@
           <t>Spokane Chiefs</t>
         </is>
       </c>
-      <c r="F1240" t="n">
-        <v/>
+      <c r="F1240" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="G1240" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1241">
@@ -41395,8 +41430,13 @@
           <t>Everett Silvertips</t>
         </is>
       </c>
-      <c r="F1241" t="n">
-        <v/>
+      <c r="F1241" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="G1241" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1242">
@@ -41423,8 +41463,13 @@
           <t>Kelowna Rockets</t>
         </is>
       </c>
-      <c r="F1242" t="n">
-        <v/>
+      <c r="F1242" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="G1242" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1243">
@@ -41451,8 +41496,13 @@
           <t>Penticton Vees</t>
         </is>
       </c>
-      <c r="F1243" t="n">
-        <v/>
+      <c r="F1243" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="G1243" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1244">
@@ -41479,7 +41529,292 @@
           <t>Seattle Thunderbirds</t>
         </is>
       </c>
-      <c r="F1244" t="n">
+      <c r="F1244" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="G1244" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="n">
+        <v>1022827</v>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>Sat, Mar 7, 2026</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="D1245" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="E1245" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="F1245" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="n">
+        <v>1022831</v>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>Sat, Mar 7, 2026</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="E1246" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="F1246" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="n">
+        <v>1022834</v>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>Sat, Mar 7, 2026</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="D1247" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="E1247" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1247" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="n">
+        <v>1022828</v>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>Sat, Mar 7, 2026</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="D1248" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="E1248" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="F1248" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="n">
+        <v>1022829</v>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>Sat, Mar 7, 2026</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="D1249" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="E1249" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="F1249" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="n">
+        <v>1022832</v>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>Sat, Mar 7, 2026</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="D1250" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="E1250" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="F1250" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="n">
+        <v>1022833</v>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>Sat, Mar 7, 2026</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="D1251" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="E1251" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="F1251" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="n">
+        <v>1022836</v>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>Sat, Mar 7, 2026</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="D1252" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="E1252" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="F1252" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="n">
+        <v>1022830</v>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>Sat, Mar 7, 2026</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="D1253" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="E1253" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="F1253" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="n">
+        <v>1022835</v>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>Sat, Mar 7, 2026</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="D1254" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="E1254" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="F1254" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1254"/>
+  <dimension ref="A1:I1258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -41562,8 +41562,13 @@
           <t>Brandon Wheat Kings</t>
         </is>
       </c>
-      <c r="F1245" t="n">
-        <v/>
+      <c r="F1245" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="G1245" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1246">
@@ -41590,8 +41595,13 @@
           <t>Lethbridge Hurricanes</t>
         </is>
       </c>
-      <c r="F1246" t="n">
-        <v/>
+      <c r="F1246" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="G1246" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1247">
@@ -41618,8 +41628,13 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1247" t="n">
-        <v/>
+      <c r="F1247" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="G1247" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1248">
@@ -41646,8 +41661,13 @@
           <t>Medicine Hat Tigers</t>
         </is>
       </c>
-      <c r="F1248" t="n">
-        <v/>
+      <c r="F1248" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="G1248" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1249">
@@ -41674,8 +41694,13 @@
           <t>Kamloops Blazers</t>
         </is>
       </c>
-      <c r="F1249" t="n">
-        <v/>
+      <c r="F1249" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="G1249" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1250">
@@ -41702,8 +41727,13 @@
           <t>Everett Silvertips</t>
         </is>
       </c>
-      <c r="F1250" t="n">
-        <v/>
+      <c r="F1250" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="G1250" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1251">
@@ -41730,8 +41760,13 @@
           <t>Prince George Cougars</t>
         </is>
       </c>
-      <c r="F1251" t="n">
-        <v/>
+      <c r="F1251" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="G1251" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1252">
@@ -41758,8 +41793,13 @@
           <t>Penticton Vees</t>
         </is>
       </c>
-      <c r="F1252" t="n">
-        <v/>
+      <c r="F1252" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="G1252" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1253">
@@ -41786,8 +41826,13 @@
           <t>Kelowna Rockets</t>
         </is>
       </c>
-      <c r="F1253" t="n">
-        <v/>
+      <c r="F1253" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="G1253" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1254">
@@ -41814,7 +41859,124 @@
           <t>Seattle Thunderbirds</t>
         </is>
       </c>
-      <c r="F1254" t="n">
+      <c r="F1254" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="G1254" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="n">
+        <v>1022837</v>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>Sun, Mar 8, 2026</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="D1255" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="E1255" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="F1255" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="n">
+        <v>1022838</v>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>Sun, Mar 8, 2026</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="D1256" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="E1256" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1256" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="n">
+        <v>1022839</v>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>Sun, Mar 8, 2026</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="D1257" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="E1257" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="F1257" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="n">
+        <v>1022840</v>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>Sun, Mar 8, 2026</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="D1258" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="E1258" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="F1258" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1258"/>
+  <dimension ref="A1:I1262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -41892,8 +41892,13 @@
           <t>Regina Pats</t>
         </is>
       </c>
-      <c r="F1255" t="n">
-        <v/>
+      <c r="F1255" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="G1255" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1256">
@@ -41920,8 +41925,13 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1256" t="n">
-        <v/>
+      <c r="F1256" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="G1256" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1257">
@@ -41948,8 +41958,13 @@
           <t>Portland Winterhawks</t>
         </is>
       </c>
-      <c r="F1257" t="n">
-        <v/>
+      <c r="F1257" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="G1257" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1258">
@@ -41976,7 +41991,124 @@
           <t>Kelowna Rockets</t>
         </is>
       </c>
-      <c r="F1258" t="n">
+      <c r="F1258" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="G1258" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="n">
+        <v>1022841</v>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>Tue, Mar 10, 2026</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="D1259" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="E1259" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="F1259" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="n">
+        <v>1022843</v>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>Tue, Mar 10, 2026</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="D1260" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="E1260" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="F1260" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="n">
+        <v>1022842</v>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>Tue, Mar 10, 2026</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="D1261" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="E1261" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="F1261" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="n">
+        <v>1022844</v>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>Tue, Mar 10, 2026</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="D1262" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="E1262" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="F1262" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1262"/>
+  <dimension ref="A1:I1269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -42024,8 +42024,13 @@
           <t>Medicine Hat Tigers</t>
         </is>
       </c>
-      <c r="F1259" t="n">
-        <v/>
+      <c r="F1259" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="G1259" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1260">
@@ -42052,8 +42057,13 @@
           <t>Red Deer Rebels</t>
         </is>
       </c>
-      <c r="F1260" t="n">
-        <v/>
+      <c r="F1260" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="G1260" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1261">
@@ -42080,8 +42090,13 @@
           <t>Prince George Cougars</t>
         </is>
       </c>
-      <c r="F1261" t="n">
-        <v/>
+      <c r="F1261" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="G1261" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1262">
@@ -42108,7 +42123,208 @@
           <t>Seattle Thunderbirds</t>
         </is>
       </c>
-      <c r="F1262" t="n">
+      <c r="F1262" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="G1262" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="n">
+        <v>1022846</v>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>Wed, Mar 11, 2026</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="D1263" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="E1263" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="F1263" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="n">
+        <v>1022845</v>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>Wed, Mar 11, 2026</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="D1264" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="E1264" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="F1264" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="n">
+        <v>1022849</v>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>Wed, Mar 11, 2026</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="D1265" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="E1265" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="F1265" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="n">
+        <v>1022851</v>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>Wed, Mar 11, 2026</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="D1266" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="E1266" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="F1266" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="n">
+        <v>1022847</v>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>Wed, Mar 11, 2026</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="D1267" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="E1267" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="F1267" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="n">
+        <v>1022848</v>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>Wed, Mar 11, 2026</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="D1268" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="E1268" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="F1268" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="n">
+        <v>1022850</v>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>Wed, Mar 11, 2026</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="D1269" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="E1269" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="F1269" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1269"/>
+  <dimension ref="A1:I1279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -42156,8 +42156,13 @@
           <t>Edmonton Oil Kings</t>
         </is>
       </c>
-      <c r="F1263" t="n">
-        <v/>
+      <c r="F1263" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="G1263" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1264">
@@ -42184,8 +42189,13 @@
           <t>Brandon Wheat Kings</t>
         </is>
       </c>
-      <c r="F1264" t="n">
-        <v/>
+      <c r="F1264" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="G1264" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1265">
@@ -42212,8 +42222,13 @@
           <t>Regina Pats</t>
         </is>
       </c>
-      <c r="F1265" t="n">
-        <v/>
+      <c r="F1265" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="G1265" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1266">
@@ -42240,8 +42255,13 @@
           <t>Moose Jaw Warriors</t>
         </is>
       </c>
-      <c r="F1266" t="n">
-        <v/>
+      <c r="F1266" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="G1266" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1267">
@@ -42268,8 +42288,13 @@
           <t>Kamloops Blazers</t>
         </is>
       </c>
-      <c r="F1267" t="n">
-        <v/>
+      <c r="F1267" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="G1267" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1268">
@@ -42296,8 +42321,13 @@
           <t>Kelowna Rockets</t>
         </is>
       </c>
-      <c r="F1268" t="n">
-        <v/>
+      <c r="F1268" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="G1268" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1269">
@@ -42324,7 +42354,292 @@
           <t>Spokane Chiefs</t>
         </is>
       </c>
-      <c r="F1269" t="n">
+      <c r="F1269" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="G1269" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="n">
+        <v>1022853</v>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>Fri, Mar 13, 2026</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="D1270" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="E1270" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="F1270" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="n">
+        <v>1022856</v>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>Fri, Mar 13, 2026</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="D1271" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="E1271" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1271" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="n">
+        <v>1022858</v>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>Fri, Mar 13, 2026</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="D1272" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="E1272" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="F1272" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="n">
+        <v>1022859</v>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>Fri, Mar 13, 2026</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="D1273" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="E1273" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="F1273" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="n">
+        <v>1022855</v>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>Fri, Mar 13, 2026</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="D1274" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="E1274" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="F1274" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="n">
+        <v>1022857</v>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>Fri, Mar 13, 2026</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="D1275" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="E1275" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="F1275" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="n">
+        <v>1022852</v>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>Fri, Mar 13, 2026</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="E1276" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="F1276" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="n">
+        <v>1022854</v>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>Fri, Mar 13, 2026</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="E1277" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="F1277" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="n">
+        <v>1022860</v>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>Fri, Mar 13, 2026</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="E1278" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="F1278" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="n">
+        <v>1022861</v>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>Fri, Mar 13, 2026</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="D1279" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="E1279" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="F1279" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1279"/>
+  <dimension ref="A1:I1290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -42387,8 +42387,13 @@
           <t>Medicine Hat Tigers</t>
         </is>
       </c>
-      <c r="F1270" t="n">
-        <v/>
+      <c r="F1270" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="G1270" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1271">
@@ -42415,8 +42420,13 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1271" t="n">
-        <v/>
+      <c r="F1271" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="G1271" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1272">
@@ -42443,8 +42453,13 @@
           <t>Brandon Wheat Kings</t>
         </is>
       </c>
-      <c r="F1272" t="n">
-        <v/>
+      <c r="F1272" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="G1272" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1273">
@@ -42471,8 +42486,13 @@
           <t>Saskatoon Blades</t>
         </is>
       </c>
-      <c r="F1273" t="n">
-        <v/>
+      <c r="F1273" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="G1273" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1274">
@@ -42499,8 +42519,13 @@
           <t>Portland Winterhawks</t>
         </is>
       </c>
-      <c r="F1274" t="n">
-        <v/>
+      <c r="F1274" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="G1274" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1275">
@@ -42527,8 +42552,13 @@
           <t>Prince George Cougars</t>
         </is>
       </c>
-      <c r="F1275" t="n">
-        <v/>
+      <c r="F1275" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="G1275" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1276">
@@ -42555,8 +42585,13 @@
           <t>Kelowna Rockets</t>
         </is>
       </c>
-      <c r="F1276" t="n">
-        <v/>
+      <c r="F1276" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="G1276" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1277">
@@ -42583,8 +42618,13 @@
           <t>Everett Silvertips</t>
         </is>
       </c>
-      <c r="F1277" t="n">
-        <v/>
+      <c r="F1277" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="G1277" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1278">
@@ -42611,8 +42651,13 @@
           <t>Spokane Chiefs</t>
         </is>
       </c>
-      <c r="F1278" t="n">
-        <v/>
+      <c r="F1278" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="G1278" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1279">
@@ -42639,7 +42684,320 @@
           <t>Victoria Royals</t>
         </is>
       </c>
-      <c r="F1279" t="n">
+      <c r="F1279" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="G1279" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="n">
+        <v>1022867</v>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>Sat, Mar 14, 2026</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="D1280" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="E1280" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="F1280" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="n">
+        <v>1022868</v>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>Sat, Mar 14, 2026</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="D1281" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="E1281" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1281" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="n">
+        <v>1022862</v>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>Sat, Mar 14, 2026</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="D1282" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="E1282" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="F1282" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="n">
+        <v>1022864</v>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>Sat, Mar 14, 2026</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="D1283" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="E1283" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="F1283" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="n">
+        <v>1022865</v>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>Sat, Mar 14, 2026</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="D1284" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="E1284" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="F1284" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="n">
+        <v>1022866</v>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>Sat, Mar 14, 2026</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="D1285" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="E1285" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="F1285" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="n">
+        <v>1022870</v>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>Sat, Mar 14, 2026</t>
+        </is>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="D1286" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="E1286" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="F1286" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="n">
+        <v>1022863</v>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>Sat, Mar 14, 2026</t>
+        </is>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="D1287" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="E1287" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="F1287" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="n">
+        <v>1022869</v>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>Sat, Mar 14, 2026</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="D1288" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="E1288" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="F1288" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="n">
+        <v>1022871</v>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>Sat, Mar 14, 2026</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="D1289" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="E1289" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="F1289" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="n">
+        <v>1022872</v>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>Sat, Mar 14, 2026</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="D1290" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="E1290" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="F1290" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1290"/>
+  <dimension ref="A1:I1294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -42717,8 +42717,13 @@
           <t>Calgary Hitmen</t>
         </is>
       </c>
-      <c r="F1280" t="n">
-        <v/>
+      <c r="F1280" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="G1280" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1281">
@@ -42745,8 +42750,13 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1281" t="n">
-        <v/>
+      <c r="F1281" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="G1281" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1282">
@@ -42773,8 +42783,13 @@
           <t>Edmonton Oil Kings</t>
         </is>
       </c>
-      <c r="F1282" t="n">
-        <v/>
+      <c r="F1282" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="G1282" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1283">
@@ -42801,8 +42816,13 @@
           <t>Kelowna Rockets</t>
         </is>
       </c>
-      <c r="F1283" t="n">
-        <v/>
+      <c r="F1283" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="G1283" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1284">
@@ -42829,8 +42849,13 @@
           <t>Medicine Hat Tigers</t>
         </is>
       </c>
-      <c r="F1284" t="n">
-        <v/>
+      <c r="F1284" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="G1284" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1285">
@@ -42857,8 +42882,13 @@
           <t>Prince George Cougars</t>
         </is>
       </c>
-      <c r="F1285" t="n">
-        <v/>
+      <c r="F1285" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="G1285" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1286">
@@ -42885,8 +42915,13 @@
           <t>Saskatoon Blades</t>
         </is>
       </c>
-      <c r="F1286" t="n">
-        <v/>
+      <c r="F1286" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="G1286" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1287">
@@ -42913,8 +42948,13 @@
           <t>Everett Silvertips</t>
         </is>
       </c>
-      <c r="F1287" t="n">
-        <v/>
+      <c r="F1287" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="G1287" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1288">
@@ -42941,8 +42981,13 @@
           <t>Portland Winterhawks</t>
         </is>
       </c>
-      <c r="F1288" t="n">
-        <v/>
+      <c r="F1288" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="G1288" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1289">
@@ -42969,8 +43014,13 @@
           <t>Spokane Chiefs</t>
         </is>
       </c>
-      <c r="F1289" t="n">
-        <v/>
+      <c r="F1289" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="G1289" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1290">
@@ -42997,7 +43047,124 @@
           <t>Victoria Royals</t>
         </is>
       </c>
-      <c r="F1290" t="n">
+      <c r="F1290" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="G1290" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="n">
+        <v>1022874</v>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>Sun, Mar 15, 2026</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="D1291" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="E1291" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="F1291" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="n">
+        <v>1022873</v>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>Sun, Mar 15, 2026</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="D1292" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="E1292" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="F1292" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="n">
+        <v>1022875</v>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>Sun, Mar 15, 2026</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="D1293" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="E1293" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="F1293" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="n">
+        <v>1022876</v>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>Sun, Mar 15, 2026</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="D1294" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="E1294" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="F1294" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1294"/>
+  <dimension ref="A1:I1298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -43080,8 +43080,13 @@
           <t>Regina Pats</t>
         </is>
       </c>
-      <c r="F1291" t="n">
-        <v/>
+      <c r="F1291" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="G1291" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1292">
@@ -43108,8 +43113,13 @@
           <t>Edmonton Oil Kings</t>
         </is>
       </c>
-      <c r="F1292" t="n">
-        <v/>
+      <c r="F1292" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="G1292" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1293">
@@ -43136,8 +43146,13 @@
           <t>Everett Silvertips</t>
         </is>
       </c>
-      <c r="F1293" t="n">
-        <v/>
+      <c r="F1293" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="G1293" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1294">
@@ -43164,7 +43179,124 @@
           <t>Seattle Thunderbirds</t>
         </is>
       </c>
-      <c r="F1294" t="n">
+      <c r="F1294" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="G1294" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="n">
+        <v>1022878</v>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>Tue, Mar 17, 2026</t>
+        </is>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="D1295" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="E1295" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1295" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="n">
+        <v>1022877</v>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>Tue, Mar 17, 2026</t>
+        </is>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="D1296" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="E1296" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="F1296" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="n">
+        <v>1022879</v>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>Tue, Mar 17, 2026</t>
+        </is>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="D1297" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="E1297" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="F1297" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="n">
+        <v>1022880</v>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>Tue, Mar 17, 2026</t>
+        </is>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="D1298" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="E1298" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="F1298" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1298"/>
+  <dimension ref="A1:I1301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -43212,8 +43212,13 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1295" t="n">
-        <v/>
+      <c r="F1295" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="G1295" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1296">
@@ -43240,8 +43245,13 @@
           <t>Penticton Vees</t>
         </is>
       </c>
-      <c r="F1296" t="n">
-        <v/>
+      <c r="F1296" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="G1296" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1297">
@@ -43268,8 +43278,13 @@
           <t>Prince George Cougars</t>
         </is>
       </c>
-      <c r="F1297" t="n">
-        <v/>
+      <c r="F1297" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="G1297" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1298">
@@ -43296,7 +43311,96 @@
           <t>Everett Silvertips</t>
         </is>
       </c>
-      <c r="F1298" t="n">
+      <c r="F1298" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="G1298" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="n">
+        <v>1022881</v>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>Wed, Mar 18, 2026</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="D1299" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="E1299" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="F1299" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="n">
+        <v>1022882</v>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>Wed, Mar 18, 2026</t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="D1300" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="E1300" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="F1300" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="n">
+        <v>1022883</v>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>Wed, Mar 18, 2026</t>
+        </is>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="D1301" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="E1301" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="F1301" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1301"/>
+  <dimension ref="A1:I1312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -43344,8 +43344,13 @@
           <t>Edmonton Oil Kings</t>
         </is>
       </c>
-      <c r="F1299" t="n">
-        <v/>
+      <c r="F1299" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="G1299" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1300">
@@ -43372,8 +43377,13 @@
           <t>Red Deer Rebels</t>
         </is>
       </c>
-      <c r="F1300" t="n">
-        <v/>
+      <c r="F1300" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="G1300" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1301">
@@ -43400,7 +43410,320 @@
           <t>Brandon Wheat Kings</t>
         </is>
       </c>
-      <c r="F1301" t="n">
+      <c r="F1301" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="G1301" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="n">
+        <v>1022885</v>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>Fri, Mar 20, 2026</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="D1302" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="E1302" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="F1302" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="n">
+        <v>1022887</v>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>Fri, Mar 20, 2026</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="D1303" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="E1303" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1303" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="n">
+        <v>1022888</v>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>Fri, Mar 20, 2026</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="D1304" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="E1304" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="F1304" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="n">
+        <v>1022889</v>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>Fri, Mar 20, 2026</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="D1305" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="E1305" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="F1305" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="n">
+        <v>1022891</v>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>Fri, Mar 20, 2026</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="D1306" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="E1306" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="F1306" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="n">
+        <v>1022884</v>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>Fri, Mar 20, 2026</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="D1307" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="E1307" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="F1307" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="n">
+        <v>1022894</v>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>Fri, Mar 20, 2026</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="D1308" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="E1308" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="F1308" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="n">
+        <v>1022886</v>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>Fri, Mar 20, 2026</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="D1309" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="E1309" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="F1309" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="n">
+        <v>1022890</v>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>Fri, Mar 20, 2026</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="D1310" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="E1310" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="F1310" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="n">
+        <v>1022892</v>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>Fri, Mar 20, 2026</t>
+        </is>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="D1311" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="E1311" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="F1311" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="n">
+        <v>1022893</v>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>Fri, Mar 20, 2026</t>
+        </is>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="D1312" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="E1312" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="F1312" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1312"/>
+  <dimension ref="A1:I1323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -43443,8 +43443,13 @@
           <t>Edmonton Oil Kings</t>
         </is>
       </c>
-      <c r="F1302" t="n">
-        <v/>
+      <c r="F1302" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="G1302" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1303">
@@ -43471,8 +43476,13 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1303" t="n">
-        <v/>
+      <c r="F1303" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="G1303" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1304">
@@ -43499,8 +43509,13 @@
           <t>Medicine Hat Tigers</t>
         </is>
       </c>
-      <c r="F1304" t="n">
-        <v/>
+      <c r="F1304" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="G1304" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1305">
@@ -43527,8 +43542,13 @@
           <t>Brandon Wheat Kings</t>
         </is>
       </c>
-      <c r="F1305" t="n">
-        <v/>
+      <c r="F1305" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="G1305" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1306">
@@ -43555,8 +43575,13 @@
           <t>Moose Jaw Warriors</t>
         </is>
       </c>
-      <c r="F1306" t="n">
-        <v/>
+      <c r="F1306" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="G1306" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1307">
@@ -43583,8 +43608,13 @@
           <t>Kamloops Blazers</t>
         </is>
       </c>
-      <c r="F1307" t="n">
-        <v/>
+      <c r="F1307" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="G1307" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1308">
@@ -43611,8 +43641,13 @@
           <t>Everett Silvertips</t>
         </is>
       </c>
-      <c r="F1308" t="n">
-        <v/>
+      <c r="F1308" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="G1308" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1309">
@@ -43639,8 +43674,13 @@
           <t>Penticton Vees</t>
         </is>
       </c>
-      <c r="F1309" t="n">
-        <v/>
+      <c r="F1309" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="G1309" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1310">
@@ -43667,8 +43707,13 @@
           <t>Spokane Chiefs</t>
         </is>
       </c>
-      <c r="F1310" t="n">
-        <v/>
+      <c r="F1310" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="G1310" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1311">
@@ -43695,8 +43740,13 @@
           <t>Portland Winterhawks</t>
         </is>
       </c>
-      <c r="F1311" t="n">
-        <v/>
+      <c r="F1311" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="G1311" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1312">
@@ -43723,7 +43773,320 @@
           <t>Prince George Cougars</t>
         </is>
       </c>
-      <c r="F1312" t="n">
+      <c r="F1312" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="G1312" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="n">
+        <v>1022895</v>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>Sat, Mar 21, 2026</t>
+        </is>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="D1313" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="E1313" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="F1313" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="n">
+        <v>1022896</v>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>Sat, Mar 21, 2026</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="D1314" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="E1314" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="F1314" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="n">
+        <v>1022900</v>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>Sat, Mar 21, 2026</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="D1315" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="E1315" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="F1315" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="n">
+        <v>1022899</v>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>Sat, Mar 21, 2026</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="E1316" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="F1316" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="n">
+        <v>1022901</v>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>Sat, Mar 21, 2026</t>
+        </is>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="E1317" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="F1317" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="n">
+        <v>1022902</v>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>Sat, Mar 21, 2026</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="D1318" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="E1318" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1318" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="n">
+        <v>1022897</v>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>Sat, Mar 21, 2026</t>
+        </is>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="D1319" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="E1319" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="F1319" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="n">
+        <v>1022898</v>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>Sat, Mar 21, 2026</t>
+        </is>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="D1320" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="E1320" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="F1320" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="n">
+        <v>1022903</v>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>Sat, Mar 21, 2026</t>
+        </is>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="D1321" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="E1321" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="F1321" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="n">
+        <v>1022905</v>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>Sat, Mar 21, 2026</t>
+        </is>
+      </c>
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="D1322" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="E1322" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="F1322" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="n">
+        <v>1022904</v>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>Sat, Mar 21, 2026</t>
+        </is>
+      </c>
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="D1323" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="E1323" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="F1323" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1323"/>
+  <dimension ref="A1:I1325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -43806,8 +43806,13 @@
           <t>Brandon Wheat Kings</t>
         </is>
       </c>
-      <c r="F1313" t="n">
-        <v/>
+      <c r="F1313" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="G1313" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1314">
@@ -43834,8 +43839,13 @@
           <t>Calgary Hitmen</t>
         </is>
       </c>
-      <c r="F1314" t="n">
-        <v/>
+      <c r="F1314" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="G1314" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1315">
@@ -43862,8 +43872,13 @@
           <t>Moose Jaw Warriors</t>
         </is>
       </c>
-      <c r="F1315" t="n">
-        <v/>
+      <c r="F1315" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="G1315" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1316">
@@ -43890,8 +43905,13 @@
           <t>Medicine Hat Tigers</t>
         </is>
       </c>
-      <c r="F1316" t="n">
-        <v/>
+      <c r="F1316" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="G1316" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1317">
@@ -43918,8 +43938,13 @@
           <t>Seattle Thunderbirds</t>
         </is>
       </c>
-      <c r="F1317" t="n">
-        <v/>
+      <c r="F1317" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="G1317" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1318">
@@ -43946,8 +43971,13 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1318" t="n">
-        <v/>
+      <c r="F1318" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="G1318" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1319">
@@ -43974,8 +44004,13 @@
           <t>Everett Silvertips</t>
         </is>
       </c>
-      <c r="F1319" t="n">
-        <v/>
+      <c r="F1319" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="G1319" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1320">
@@ -44002,8 +44037,13 @@
           <t>Penticton Vees</t>
         </is>
       </c>
-      <c r="F1320" t="n">
-        <v/>
+      <c r="F1320" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="G1320" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1321">
@@ -44030,8 +44070,13 @@
           <t>Spokane Chiefs</t>
         </is>
       </c>
-      <c r="F1321" t="n">
-        <v/>
+      <c r="F1321" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="G1321" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1322">
@@ -44058,8 +44103,13 @@
           <t>Prince George Cougars</t>
         </is>
       </c>
-      <c r="F1322" t="n">
-        <v/>
+      <c r="F1322" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="G1322" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1323">
@@ -44086,7 +44136,68 @@
           <t>Kamloops Blazers</t>
         </is>
       </c>
-      <c r="F1323" t="n">
+      <c r="F1323" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="G1323" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="n">
+        <v>1022906</v>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>Sun, Mar 22, 2026</t>
+        </is>
+      </c>
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="D1324" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="E1324" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="F1324" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="n">
+        <v>1022907</v>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>Sun, Mar 22, 2026</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="D1325" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="E1325" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="F1325" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1325"/>
+  <dimension ref="A1:I1333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -44169,8 +44169,13 @@
           <t>Calgary Hitmen</t>
         </is>
       </c>
-      <c r="F1324" t="n">
-        <v/>
+      <c r="F1324" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="G1324" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1325">
@@ -44197,7 +44202,236 @@
           <t>Spokane Chiefs</t>
         </is>
       </c>
-      <c r="F1325" t="n">
+      <c r="F1325" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="G1325" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="n">
+        <v>1022925</v>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>Fri, Mar 27, 2026</t>
+        </is>
+      </c>
+      <c r="C1326" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="D1326" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="E1326" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1326" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="n">
+        <v>1022927</v>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>Fri, Mar 27, 2026</t>
+        </is>
+      </c>
+      <c r="C1327" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="D1327" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="E1327" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="F1327" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="n">
+        <v>1022929</v>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>Fri, Mar 27, 2026</t>
+        </is>
+      </c>
+      <c r="C1328" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="D1328" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="E1328" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="F1328" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="n">
+        <v>1022956</v>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>Fri, Mar 27, 2026</t>
+        </is>
+      </c>
+      <c r="C1329" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="D1329" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="E1329" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="F1329" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="n">
+        <v>1022963</v>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>Fri, Mar 27, 2026</t>
+        </is>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="D1330" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="E1330" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="F1330" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="n">
+        <v>1022919</v>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>Fri, Mar 27, 2026</t>
+        </is>
+      </c>
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="D1331" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="E1331" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="F1331" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="n">
+        <v>1022921</v>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>Fri, Mar 27, 2026</t>
+        </is>
+      </c>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="D1332" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="E1332" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="F1332" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="n">
+        <v>1022923</v>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>Fri, Mar 27, 2026</t>
+        </is>
+      </c>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="D1333" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="E1333" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="F1333" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1333"/>
+  <dimension ref="A1:I1339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -44235,8 +44235,13 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1326" t="n">
-        <v/>
+      <c r="F1326" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="G1326" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1327">
@@ -44263,8 +44268,13 @@
           <t>Edmonton Oil Kings</t>
         </is>
       </c>
-      <c r="F1327" t="n">
-        <v/>
+      <c r="F1327" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="G1327" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1328">
@@ -44291,8 +44301,13 @@
           <t>Brandon Wheat Kings</t>
         </is>
       </c>
-      <c r="F1328" t="n">
-        <v/>
+      <c r="F1328" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="G1328" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1329">
@@ -44319,8 +44334,13 @@
           <t>Medicine Hat Tigers</t>
         </is>
       </c>
-      <c r="F1329" t="n">
-        <v/>
+      <c r="F1329" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="G1329" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1330">
@@ -44347,8 +44367,13 @@
           <t>Prince George Cougars</t>
         </is>
       </c>
-      <c r="F1330" t="n">
-        <v/>
+      <c r="F1330" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="G1330" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1331">
@@ -44375,8 +44400,13 @@
           <t>Everett Silvertips</t>
         </is>
       </c>
-      <c r="F1331" t="n">
-        <v/>
+      <c r="F1331" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="G1331" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1332">
@@ -44403,8 +44433,13 @@
           <t>Kamloops Blazers</t>
         </is>
       </c>
-      <c r="F1332" t="n">
-        <v/>
+      <c r="F1332" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="G1332" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1333">
@@ -44431,7 +44466,180 @@
           <t>Penticton Vees</t>
         </is>
       </c>
-      <c r="F1333" t="n">
+      <c r="F1333" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="G1333" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="n">
+        <v>1022926</v>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>Sat, Mar 28, 2026</t>
+        </is>
+      </c>
+      <c r="C1334" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="D1334" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="E1334" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1334" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="n">
+        <v>1022957</v>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>Sat, Mar 28, 2026</t>
+        </is>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="D1335" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="E1335" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="F1335" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="n">
+        <v>1022964</v>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>Sat, Mar 28, 2026</t>
+        </is>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="D1336" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="E1336" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="F1336" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="n">
+        <v>1022920</v>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>Sat, Mar 28, 2026</t>
+        </is>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="D1337" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="E1337" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="F1337" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="n">
+        <v>1022922</v>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>Sat, Mar 28, 2026</t>
+        </is>
+      </c>
+      <c r="C1338" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="D1338" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="E1338" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="F1338" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="n">
+        <v>1022924</v>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>Sat, Mar 28, 2026</t>
+        </is>
+      </c>
+      <c r="C1339" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="D1339" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="E1339" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="F1339" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1339"/>
+  <dimension ref="A1:I1341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -44499,8 +44499,13 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1334" t="n">
-        <v/>
+      <c r="F1334" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="G1334" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1335">
@@ -44527,8 +44532,13 @@
           <t>Medicine Hat Tigers</t>
         </is>
       </c>
-      <c r="F1335" t="n">
-        <v/>
+      <c r="F1335" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="G1335" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1336">
@@ -44555,8 +44565,13 @@
           <t>Prince George Cougars</t>
         </is>
       </c>
-      <c r="F1336" t="n">
-        <v/>
+      <c r="F1336" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="G1336" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1337">
@@ -44583,8 +44598,13 @@
           <t>Everett Silvertips</t>
         </is>
       </c>
-      <c r="F1337" t="n">
-        <v/>
+      <c r="F1337" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="G1337" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1338">
@@ -44611,8 +44631,13 @@
           <t>Kelowna Rockets</t>
         </is>
       </c>
-      <c r="F1338" t="n">
-        <v/>
+      <c r="F1338" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="G1338" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1339">
@@ -44639,7 +44664,68 @@
           <t>Penticton Vees</t>
         </is>
       </c>
-      <c r="F1339" t="n">
+      <c r="F1339" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="G1339" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="n">
+        <v>1022928</v>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>Sun, Mar 29, 2026</t>
+        </is>
+      </c>
+      <c r="C1340" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="D1340" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="E1340" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="F1340" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="n">
+        <v>1022930</v>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>Sun, Mar 29, 2026</t>
+        </is>
+      </c>
+      <c r="C1341" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="D1341" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="E1341" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="F1341" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1341"/>
+  <dimension ref="A1:I1342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -44697,8 +44697,13 @@
           <t>Edmonton Oil Kings</t>
         </is>
       </c>
-      <c r="F1340" t="n">
-        <v/>
+      <c r="F1340" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="G1340" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1341">
@@ -44725,7 +44730,40 @@
           <t>Calgary Hitmen</t>
         </is>
       </c>
-      <c r="F1341" t="n">
+      <c r="F1341" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="G1341" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="n">
+        <v>1022967</v>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>Mon, Mar 30, 2026</t>
+        </is>
+      </c>
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="D1342" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="E1342" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="F1342" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1342"/>
+  <dimension ref="A1:I1349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -44763,7 +44763,208 @@
           <t>Prince George Cougars</t>
         </is>
       </c>
-      <c r="F1342" t="n">
+      <c r="F1342" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="G1342" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="n">
+        <v>1022931</v>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>Tue, Mar 31, 2026</t>
+        </is>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="D1343" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="E1343" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="F1343" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="n">
+        <v>1022936</v>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>Tue, Mar 31, 2026</t>
+        </is>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="D1344" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="E1344" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="F1344" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="n">
+        <v>1022951</v>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>Tue, Mar 31, 2026</t>
+        </is>
+      </c>
+      <c r="C1345" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="D1345" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="E1345" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1345" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="n">
+        <v>1022958</v>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>Tue, Mar 31, 2026</t>
+        </is>
+      </c>
+      <c r="C1346" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="D1346" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="E1346" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="F1346" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="n">
+        <v>1022946</v>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t>Tue, Mar 31, 2026</t>
+        </is>
+      </c>
+      <c r="C1347" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="D1347" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="E1347" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="F1347" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="n">
+        <v>1022965</v>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>Tue, Mar 31, 2026</t>
+        </is>
+      </c>
+      <c r="C1348" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="D1348" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="E1348" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="F1348" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="n">
+        <v>1022941</v>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>Tue, Mar 31, 2026</t>
+        </is>
+      </c>
+      <c r="C1349" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="D1349" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="E1349" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="F1349" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1349"/>
+  <dimension ref="A1:I1356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -44796,8 +44796,13 @@
           <t>Calgary Hitmen</t>
         </is>
       </c>
-      <c r="F1343" t="n">
-        <v/>
+      <c r="F1343" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="G1343" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1344">
@@ -44824,8 +44829,13 @@
           <t>Edmonton Oil Kings</t>
         </is>
       </c>
-      <c r="F1344" t="n">
-        <v/>
+      <c r="F1344" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="G1344" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1345">
@@ -44852,8 +44862,13 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1345" t="n">
-        <v/>
+      <c r="F1345" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="G1345" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1346">
@@ -44880,8 +44895,13 @@
           <t>Medicine Hat Tigers</t>
         </is>
       </c>
-      <c r="F1346" t="n">
-        <v/>
+      <c r="F1346" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="G1346" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1347">
@@ -44908,8 +44928,13 @@
           <t>Everett Silvertips</t>
         </is>
       </c>
-      <c r="F1347" t="n">
-        <v/>
+      <c r="F1347" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="G1347" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1348">
@@ -44936,8 +44961,13 @@
           <t>Kelowna Rockets</t>
         </is>
       </c>
-      <c r="F1348" t="n">
-        <v/>
+      <c r="F1348" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="G1348" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1349">
@@ -44964,7 +44994,208 @@
           <t>Penticton Vees</t>
         </is>
       </c>
-      <c r="F1349" t="n">
+      <c r="F1349" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="G1349" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="n">
+        <v>1022937</v>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>Wed, Apr 1, 2026</t>
+        </is>
+      </c>
+      <c r="C1350" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="D1350" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="E1350" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="F1350" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="n">
+        <v>1022952</v>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>Wed, Apr 1, 2026</t>
+        </is>
+      </c>
+      <c r="C1351" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="D1351" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="E1351" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1351" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="n">
+        <v>1022959</v>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>Wed, Apr 1, 2026</t>
+        </is>
+      </c>
+      <c r="C1352" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="D1352" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="E1352" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="F1352" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="n">
+        <v>1022947</v>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>Wed, Apr 1, 2026</t>
+        </is>
+      </c>
+      <c r="C1353" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="D1353" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="E1353" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="F1353" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="n">
+        <v>1022966</v>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>Wed, Apr 1, 2026</t>
+        </is>
+      </c>
+      <c r="C1354" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="D1354" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="E1354" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="F1354" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="n">
+        <v>1022942</v>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>Wed, Apr 1, 2026</t>
+        </is>
+      </c>
+      <c r="C1355" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="D1355" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="E1355" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="F1355" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="n">
+        <v>1022968</v>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>Wed, Apr 1, 2026</t>
+        </is>
+      </c>
+      <c r="C1356" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="D1356" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="E1356" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="F1356" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1356"/>
+  <dimension ref="A1:I1358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -45027,8 +45027,13 @@
           <t>Edmonton Oil Kings</t>
         </is>
       </c>
-      <c r="F1350" t="n">
-        <v/>
+      <c r="F1350" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="G1350" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1351">
@@ -45055,8 +45060,13 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1351" t="n">
-        <v/>
+      <c r="F1351" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="G1351" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1352">
@@ -45083,8 +45093,13 @@
           <t>Medicine Hat Tigers</t>
         </is>
       </c>
-      <c r="F1352" t="n">
-        <v/>
+      <c r="F1352" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="G1352" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1353">
@@ -45111,8 +45126,13 @@
           <t>Everett Silvertips</t>
         </is>
       </c>
-      <c r="F1353" t="n">
-        <v/>
+      <c r="F1353" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="G1353" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1354">
@@ -45139,8 +45159,13 @@
           <t>Kelowna Rockets</t>
         </is>
       </c>
-      <c r="F1354" t="n">
-        <v/>
+      <c r="F1354" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="G1354" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1355">
@@ -45167,8 +45192,13 @@
           <t>Penticton Vees</t>
         </is>
       </c>
-      <c r="F1355" t="n">
-        <v/>
+      <c r="F1355" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="G1355" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1356">
@@ -45195,7 +45225,68 @@
           <t>Prince George Cougars</t>
         </is>
       </c>
-      <c r="F1356" t="n">
+      <c r="F1356" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="G1356" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="n">
+        <v>1022932</v>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>Thu, Apr 2, 2026</t>
+        </is>
+      </c>
+      <c r="C1357" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="D1357" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="E1357" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="F1357" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="n">
+        <v>1022972</v>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>Thu, Apr 2, 2026</t>
+        </is>
+      </c>
+      <c r="C1358" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="D1358" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="E1358" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="F1358" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1358"/>
+  <dimension ref="A1:I1361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -45258,8 +45258,13 @@
           <t>Calgary Hitmen</t>
         </is>
       </c>
-      <c r="F1357" t="n">
-        <v/>
+      <c r="F1357" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="G1357" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1358">
@@ -45286,7 +45291,96 @@
           <t>Spokane Chiefs</t>
         </is>
       </c>
-      <c r="F1358" t="n">
+      <c r="F1358" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="G1358" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="n">
+        <v>1022938</v>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>Fri, Apr 3, 2026</t>
+        </is>
+      </c>
+      <c r="C1359" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="D1359" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="E1359" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="F1359" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="n">
+        <v>1022953</v>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>Fri, Apr 3, 2026</t>
+        </is>
+      </c>
+      <c r="C1360" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="D1360" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="E1360" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1360" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="n">
+        <v>1022943</v>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>Fri, Apr 3, 2026</t>
+        </is>
+      </c>
+      <c r="C1361" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="D1361" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="E1361" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="F1361" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1361"/>
+  <dimension ref="A1:I1362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -45324,8 +45324,13 @@
           <t>Edmonton Oil Kings</t>
         </is>
       </c>
-      <c r="F1359" t="n">
-        <v/>
+      <c r="F1359" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="G1359" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1360">
@@ -45352,8 +45357,13 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1360" t="n">
-        <v/>
+      <c r="F1360" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="G1360" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1361">
@@ -45380,7 +45390,40 @@
           <t>Penticton Vees</t>
         </is>
       </c>
-      <c r="F1361" t="n">
+      <c r="F1361" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="G1361" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="n">
+        <v>1022960</v>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>Sat, Apr 4, 2026</t>
+        </is>
+      </c>
+      <c r="C1362" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="D1362" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="E1362" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="F1362" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1362"/>
+  <dimension ref="A1:I1364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -45423,7 +45423,68 @@
           <t>Medicine Hat Tigers</t>
         </is>
       </c>
-      <c r="F1362" t="n">
+      <c r="F1362" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="G1362" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="n">
+        <v>1022939</v>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>Sun, Apr 5, 2026</t>
+        </is>
+      </c>
+      <c r="C1363" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="D1363" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="E1363" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="F1363" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="n">
+        <v>1022973</v>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>Sun, Apr 5, 2026</t>
+        </is>
+      </c>
+      <c r="C1364" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="D1364" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="E1364" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="F1364" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1364"/>
+  <dimension ref="A1:I1365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -45456,8 +45456,13 @@
           <t>Edmonton Oil Kings</t>
         </is>
       </c>
-      <c r="F1363" t="n">
-        <v/>
+      <c r="F1363" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="G1363" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1364">
@@ -45484,7 +45489,40 @@
           <t>Spokane Chiefs</t>
         </is>
       </c>
-      <c r="F1364" t="n">
+      <c r="F1364" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="G1364" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="n">
+        <v>1022940</v>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>Mon, Apr 6, 2026</t>
+        </is>
+      </c>
+      <c r="C1365" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="D1365" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="E1365" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="F1365" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1365"/>
+  <dimension ref="A1:I1369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -45522,7 +45522,124 @@
           <t>Edmonton Oil Kings</t>
         </is>
       </c>
-      <c r="F1365" t="n">
+      <c r="F1365" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="G1365" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="n">
+        <v>1022989</v>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>Fri, Apr 10, 2026</t>
+        </is>
+      </c>
+      <c r="C1366" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="D1366" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="E1366" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1366" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="n">
+        <v>1022996</v>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>Fri, Apr 10, 2026</t>
+        </is>
+      </c>
+      <c r="C1367" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="D1367" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="E1367" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="F1367" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="n">
+        <v>1022975</v>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>Fri, Apr 10, 2026</t>
+        </is>
+      </c>
+      <c r="C1368" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="D1368" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="E1368" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="F1368" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="n">
+        <v>1022982</v>
+      </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t>Fri, Apr 10, 2026</t>
+        </is>
+      </c>
+      <c r="C1369" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="D1369" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="E1369" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="F1369" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1369"/>
+  <dimension ref="A1:I1373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -45555,8 +45555,13 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1366" t="n">
-        <v/>
+      <c r="F1366" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="G1366" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1367">
@@ -45583,8 +45588,13 @@
           <t>Medicine Hat Tigers</t>
         </is>
       </c>
-      <c r="F1367" t="n">
-        <v/>
+      <c r="F1367" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="G1367" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1368">
@@ -45611,8 +45621,13 @@
           <t>Everett Silvertips</t>
         </is>
       </c>
-      <c r="F1368" t="n">
-        <v/>
+      <c r="F1368" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="G1368" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1369">
@@ -45639,7 +45654,124 @@
           <t>Prince George Cougars</t>
         </is>
       </c>
-      <c r="F1369" t="n">
+      <c r="F1369" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="G1369" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="n">
+        <v>1022990</v>
+      </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t>Sat, Apr 11, 2026</t>
+        </is>
+      </c>
+      <c r="C1370" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="D1370" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="E1370" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1370" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="n">
+        <v>1022997</v>
+      </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t>Sat, Apr 11, 2026</t>
+        </is>
+      </c>
+      <c r="C1371" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="D1371" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="E1371" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="F1371" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="n">
+        <v>1022976</v>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t>Sat, Apr 11, 2026</t>
+        </is>
+      </c>
+      <c r="C1372" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="D1372" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="E1372" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="F1372" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="n">
+        <v>1022983</v>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t>Sat, Apr 11, 2026</t>
+        </is>
+      </c>
+      <c r="C1373" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="D1373" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="E1373" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="F1373" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1373"/>
+  <dimension ref="A1:I1374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -45687,8 +45687,13 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1370" t="n">
-        <v/>
+      <c r="F1370" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="G1370" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1371">
@@ -45715,8 +45720,13 @@
           <t>Medicine Hat Tigers</t>
         </is>
       </c>
-      <c r="F1371" t="n">
-        <v/>
+      <c r="F1371" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="G1371" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1372">
@@ -45743,8 +45753,13 @@
           <t>Everett Silvertips</t>
         </is>
       </c>
-      <c r="F1372" t="n">
-        <v/>
+      <c r="F1372" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="G1372" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1373">
@@ -45771,7 +45786,40 @@
           <t>Prince George Cougars</t>
         </is>
       </c>
-      <c r="F1373" t="n">
+      <c r="F1373" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="G1373" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="n">
+        <v>1022998</v>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>Mon, Apr 13, 2026</t>
+        </is>
+      </c>
+      <c r="C1374" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="D1374" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="E1374" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="F1374" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1374"/>
+  <dimension ref="A1:I1377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -45819,7 +45819,96 @@
           <t>Medicine Hat Tigers</t>
         </is>
       </c>
-      <c r="F1374" t="n">
+      <c r="F1374" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="G1374" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="n">
+        <v>1022991</v>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t>Tue, Apr 14, 2026</t>
+        </is>
+      </c>
+      <c r="C1375" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="D1375" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="E1375" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1375" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="n">
+        <v>1022984</v>
+      </c>
+      <c r="B1376" t="inlineStr">
+        <is>
+          <t>Tue, Apr 14, 2026</t>
+        </is>
+      </c>
+      <c r="C1376" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="D1376" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="E1376" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="F1376" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="n">
+        <v>1022977</v>
+      </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t>Tue, Apr 14, 2026</t>
+        </is>
+      </c>
+      <c r="C1377" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="D1377" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="E1377" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="F1377" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1377"/>
+  <dimension ref="A1:I1381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -45852,8 +45852,13 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1375" t="n">
-        <v/>
+      <c r="F1375" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="G1375" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1376">
@@ -45880,8 +45885,13 @@
           <t>Prince George Cougars</t>
         </is>
       </c>
-      <c r="F1376" t="n">
-        <v/>
+      <c r="F1376" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="G1376" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1377">
@@ -45908,7 +45918,124 @@
           <t>Everett Silvertips</t>
         </is>
       </c>
-      <c r="F1377" t="n">
+      <c r="F1377" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="G1377" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="n">
+        <v>1022992</v>
+      </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t>Wed, Apr 15, 2026</t>
+        </is>
+      </c>
+      <c r="C1378" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="D1378" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="E1378" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1378" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="n">
+        <v>1022999</v>
+      </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t>Wed, Apr 15, 2026</t>
+        </is>
+      </c>
+      <c r="C1379" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="D1379" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="E1379" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="F1379" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="n">
+        <v>1022985</v>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>Wed, Apr 15, 2026</t>
+        </is>
+      </c>
+      <c r="C1380" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="D1380" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="E1380" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="F1380" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="n">
+        <v>1022978</v>
+      </c>
+      <c r="B1381" t="inlineStr">
+        <is>
+          <t>Wed, Apr 15, 2026</t>
+        </is>
+      </c>
+      <c r="C1381" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="D1381" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="E1381" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="F1381" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1381"/>
+  <dimension ref="A1:I1383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -45951,8 +45951,13 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1378" t="n">
-        <v/>
+      <c r="F1378" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="G1378" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1379">
@@ -45979,8 +45984,13 @@
           <t>Medicine Hat Tigers</t>
         </is>
       </c>
-      <c r="F1379" t="n">
-        <v/>
+      <c r="F1379" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="G1379" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1380">
@@ -46007,8 +46017,13 @@
           <t>Prince George Cougars</t>
         </is>
       </c>
-      <c r="F1380" t="n">
-        <v/>
+      <c r="F1380" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="G1380" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1381">
@@ -46035,7 +46050,68 @@
           <t>Everett Silvertips</t>
         </is>
       </c>
-      <c r="F1381" t="n">
+      <c r="F1381" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="G1381" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="n">
+        <v>1022979</v>
+      </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t>Fri, Apr 17, 2026</t>
+        </is>
+      </c>
+      <c r="C1382" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="D1382" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="E1382" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="F1382" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="n">
+        <v>1022986</v>
+      </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t>Fri, Apr 17, 2026</t>
+        </is>
+      </c>
+      <c r="C1383" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="D1383" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="E1383" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="F1383" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1383"/>
+  <dimension ref="A1:I1385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -46083,8 +46083,13 @@
           <t>Everett Silvertips</t>
         </is>
       </c>
-      <c r="F1382" t="n">
-        <v/>
+      <c r="F1382" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="G1382" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1383">
@@ -46111,7 +46116,68 @@
           <t>Prince George Cougars</t>
         </is>
       </c>
-      <c r="F1383" t="n">
+      <c r="F1383" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="G1383" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="n">
+        <v>1022980</v>
+      </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t>Sun, Apr 19, 2026</t>
+        </is>
+      </c>
+      <c r="C1384" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="D1384" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="E1384" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="F1384" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="n">
+        <v>1022987</v>
+      </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t>Sun, Apr 19, 2026</t>
+        </is>
+      </c>
+      <c r="C1385" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="D1385" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="E1385" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="F1385" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1385"/>
+  <dimension ref="A1:I1386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -46177,7 +46177,40 @@
           <t>Penticton Vees</t>
         </is>
       </c>
-      <c r="F1385" t="n">
+      <c r="F1385" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="G1385" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="n">
+        <v>1023003</v>
+      </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t>Fri, Apr 24, 2026</t>
+        </is>
+      </c>
+      <c r="C1386" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="D1386" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="E1386" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1386" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1386"/>
+  <dimension ref="A1:I1387"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -46214,6 +46214,34 @@
         <v/>
       </c>
     </row>
+    <row r="1387">
+      <c r="A1387" t="n">
+        <v>1023011</v>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>Thu, Apr 23, 2026</t>
+        </is>
+      </c>
+      <c r="C1387" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="D1387" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="E1387" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="F1387" t="n">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -46238,8 +46238,13 @@
           <t>Everett Silvertips</t>
         </is>
       </c>
-      <c r="F1387" t="n">
-        <v/>
+      <c r="F1387" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="G1387" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1387"/>
+  <dimension ref="A1:I1389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -46210,8 +46210,13 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1386" t="n">
-        <v/>
+      <c r="F1386" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="G1386" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1387">
@@ -46245,6 +46250,62 @@
       </c>
       <c r="G1387" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="n">
+        <v>1023004</v>
+      </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t>Sat, Apr 25, 2026</t>
+        </is>
+      </c>
+      <c r="C1388" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="D1388" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="E1388" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1388" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="n">
+        <v>1023012</v>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>Sat, Apr 25, 2026</t>
+        </is>
+      </c>
+      <c r="C1389" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="D1389" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="E1389" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="F1389" t="n">
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1389"/>
+  <dimension ref="A1:I1390"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -46276,8 +46276,13 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1388" t="n">
-        <v/>
+      <c r="F1388" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="G1388" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1389">
@@ -46304,7 +46309,40 @@
           <t>Everett Silvertips</t>
         </is>
       </c>
-      <c r="F1389" t="n">
+      <c r="F1389" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="G1389" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="n">
+        <v>1023013</v>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>Mon, Apr 27, 2026</t>
+        </is>
+      </c>
+      <c r="C1390" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="D1390" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="E1390" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="F1390" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1390"/>
+  <dimension ref="A1:I1392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -46342,7 +46342,68 @@
           <t>Everett Silvertips</t>
         </is>
       </c>
-      <c r="F1390" t="n">
+      <c r="F1390" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="G1390" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="n">
+        <v>1023005</v>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>Tue, Apr 28, 2026</t>
+        </is>
+      </c>
+      <c r="C1391" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="D1391" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="E1391" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1391" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="n">
+        <v>1023014</v>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>Tue, Apr 28, 2026</t>
+        </is>
+      </c>
+      <c r="C1392" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="D1392" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="E1392" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="F1392" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1392"/>
+  <dimension ref="A1:I1393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -46375,8 +46375,13 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1391" t="n">
-        <v/>
+      <c r="F1391" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="G1391" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1392">
@@ -46403,7 +46408,40 @@
           <t>Everett Silvertips</t>
         </is>
       </c>
-      <c r="F1392" t="n">
+      <c r="F1392" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="G1392" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="n">
+        <v>1023006</v>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>Wed, Apr 29, 2026</t>
+        </is>
+      </c>
+      <c r="C1393" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="D1393" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="E1393" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1393" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1393"/>
+  <dimension ref="A1:I1394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -46441,7 +46441,40 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1393" t="n">
+      <c r="F1393" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="G1393" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="n">
+        <v>1023007</v>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>Fri, May 1, 2026</t>
+        </is>
+      </c>
+      <c r="C1394" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="D1394" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="E1394" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1394" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1394"/>
+  <dimension ref="A1:I1395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -46474,7 +46474,40 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1394" t="n">
+      <c r="F1394" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="G1394" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="n">
+        <v>1023008</v>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>Sun, May 3, 2026</t>
+        </is>
+      </c>
+      <c r="C1395" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="D1395" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="E1395" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1395" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -46507,8 +46507,13 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1395" t="n">
-        <v/>
+      <c r="F1395" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="G1395" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1395"/>
+  <dimension ref="A1:I1396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -46516,6 +46516,34 @@
         <v>1</v>
       </c>
     </row>
+    <row r="1396">
+      <c r="A1396" t="n">
+        <v>1023018</v>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>Fri, May 8, 2026</t>
+        </is>
+      </c>
+      <c r="C1396" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="D1396" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="E1396" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1396" t="n">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1396"/>
+  <dimension ref="A1:I1397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -46540,7 +46540,40 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1396" t="n">
+      <c r="F1396" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="G1396" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="n">
+        <v>1023019</v>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>Sat, May 9, 2026</t>
+        </is>
+      </c>
+      <c r="C1397" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="D1397" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="E1397" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1397" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1397"/>
+  <dimension ref="A1:I1398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -46573,7 +46573,40 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1397" t="n">
+      <c r="F1397" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="G1397" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="n">
+        <v>1023020</v>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>Tue, May 12, 2026</t>
+        </is>
+      </c>
+      <c r="C1398" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="D1398" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="E1398" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1398" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1398"/>
+  <dimension ref="A1:I1399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -46606,7 +46606,40 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1398" t="n">
+      <c r="F1398" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="G1398" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="n">
+        <v>1023021</v>
+      </c>
+      <c r="B1399" t="inlineStr">
+        <is>
+          <t>Wed, May 13, 2026</t>
+        </is>
+      </c>
+      <c r="C1399" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="D1399" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="E1399" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1399" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1399"/>
+  <dimension ref="A1:I1400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -46639,7 +46639,40 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1399" t="n">
+      <c r="F1399" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="G1399" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="n">
+        <v>1023022</v>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t>Fri, May 15, 2026</t>
+        </is>
+      </c>
+      <c r="C1400" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="D1400" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="E1400" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="F1400" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -46672,8 +46672,13 @@
           <t>Everett Silvertips</t>
         </is>
       </c>
-      <c r="F1400" t="n">
-        <v/>
+      <c r="F1400" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="G1400" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1400"/>
+  <dimension ref="A1:I1402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -46681,6 +46681,62 @@
         <v>1</v>
       </c>
     </row>
+    <row r="1401">
+      <c r="A1401" t="n">
+        <v>1023025</v>
+      </c>
+      <c r="B1401" t="inlineStr">
+        <is>
+          <t>Sun, Aug 30, 2026</t>
+        </is>
+      </c>
+      <c r="C1401" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="D1401" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="E1401" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="F1401" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="n">
+        <v>1023026</v>
+      </c>
+      <c r="B1402" t="inlineStr">
+        <is>
+          <t>Sun, Aug 30, 2026</t>
+        </is>
+      </c>
+      <c r="C1402" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="D1402" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="E1402" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="F1402" t="n">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1402"/>
+  <dimension ref="A1:I1403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -46705,8 +46705,13 @@
           <t>Everett Silvertips</t>
         </is>
       </c>
-      <c r="F1401" t="n">
-        <v/>
+      <c r="F1401" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="G1401" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1402">
@@ -46733,7 +46738,40 @@
           <t>Portland Winterhawks</t>
         </is>
       </c>
-      <c r="F1402" t="n">
+      <c r="F1402" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="G1402" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="n">
+        <v>1023027</v>
+      </c>
+      <c r="B1403" t="inlineStr">
+        <is>
+          <t>Mon, Aug 31, 2026</t>
+        </is>
+      </c>
+      <c r="C1403" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="D1403" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="E1403" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="F1403" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1403"/>
+  <dimension ref="A1:I1406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -46771,7 +46771,96 @@
           <t>Wenatchee Wild</t>
         </is>
       </c>
-      <c r="F1403" t="n">
+      <c r="F1403" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="G1403" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="n">
+        <v>1023029</v>
+      </c>
+      <c r="B1404" t="inlineStr">
+        <is>
+          <t>Tue, Sep 1, 2026</t>
+        </is>
+      </c>
+      <c r="C1404" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="D1404" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="E1404" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1404" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="n">
+        <v>1023028</v>
+      </c>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t>Tue, Sep 1, 2026</t>
+        </is>
+      </c>
+      <c r="C1405" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="D1405" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="E1405" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="F1405" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="n">
+        <v>1023030</v>
+      </c>
+      <c r="B1406" t="inlineStr">
+        <is>
+          <t>Tue, Sep 1, 2026</t>
+        </is>
+      </c>
+      <c r="C1406" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="D1406" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="E1406" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="F1406" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1406"/>
+  <dimension ref="A1:I1408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -46804,8 +46804,13 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1404" t="n">
-        <v/>
+      <c r="F1404" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="G1404" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1405">
@@ -46832,8 +46837,13 @@
           <t>Medicine Hat Tigers</t>
         </is>
       </c>
-      <c r="F1405" t="n">
-        <v/>
+      <c r="F1405" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="G1405" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1406">
@@ -46860,7 +46870,68 @@
           <t>Swift Current Broncos</t>
         </is>
       </c>
-      <c r="F1406" t="n">
+      <c r="F1406" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="G1406" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="n">
+        <v>1023032</v>
+      </c>
+      <c r="B1407" t="inlineStr">
+        <is>
+          <t>Wed, Sep 2, 2026</t>
+        </is>
+      </c>
+      <c r="C1407" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="D1407" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="E1407" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="F1407" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="n">
+        <v>1023031</v>
+      </c>
+      <c r="B1408" t="inlineStr">
+        <is>
+          <t>Wed, Sep 2, 2026</t>
+        </is>
+      </c>
+      <c r="C1408" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="D1408" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="E1408" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="F1408" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1408"/>
+  <dimension ref="A1:I1418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -46903,8 +46903,13 @@
           <t>Moose Jaw Warriors</t>
         </is>
       </c>
-      <c r="F1407" t="n">
-        <v/>
+      <c r="F1407" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="G1407" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1408">
@@ -46931,7 +46936,292 @@
           <t>Penticton Vees</t>
         </is>
       </c>
-      <c r="F1408" t="n">
+      <c r="F1408" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="G1408" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="n">
+        <v>1023040</v>
+      </c>
+      <c r="B1409" t="inlineStr">
+        <is>
+          <t>Fri, Sep 4, 2026</t>
+        </is>
+      </c>
+      <c r="C1409" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="D1409" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="E1409" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="F1409" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="n">
+        <v>1023037</v>
+      </c>
+      <c r="B1410" t="inlineStr">
+        <is>
+          <t>Fri, Sep 4, 2026</t>
+        </is>
+      </c>
+      <c r="C1410" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="D1410" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="E1410" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="F1410" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="n">
+        <v>1023033</v>
+      </c>
+      <c r="B1411" t="inlineStr">
+        <is>
+          <t>Fri, Sep 4, 2026</t>
+        </is>
+      </c>
+      <c r="C1411" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="D1411" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="E1411" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="F1411" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="n">
+        <v>1023034</v>
+      </c>
+      <c r="B1412" t="inlineStr">
+        <is>
+          <t>Fri, Sep 4, 2026</t>
+        </is>
+      </c>
+      <c r="C1412" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="D1412" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="E1412" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="F1412" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="n">
+        <v>1023038</v>
+      </c>
+      <c r="B1413" t="inlineStr">
+        <is>
+          <t>Fri, Sep 4, 2026</t>
+        </is>
+      </c>
+      <c r="C1413" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="D1413" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="E1413" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1413" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="n">
+        <v>1023041</v>
+      </c>
+      <c r="B1414" t="inlineStr">
+        <is>
+          <t>Fri, Sep 4, 2026</t>
+        </is>
+      </c>
+      <c r="C1414" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="D1414" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="E1414" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="F1414" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="n">
+        <v>1023035</v>
+      </c>
+      <c r="B1415" t="inlineStr">
+        <is>
+          <t>Fri, Sep 4, 2026</t>
+        </is>
+      </c>
+      <c r="C1415" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="D1415" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="E1415" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="F1415" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="n">
+        <v>1023036</v>
+      </c>
+      <c r="B1416" t="inlineStr">
+        <is>
+          <t>Fri, Sep 4, 2026</t>
+        </is>
+      </c>
+      <c r="C1416" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="D1416" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="E1416" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="F1416" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="n">
+        <v>1023039</v>
+      </c>
+      <c r="B1417" t="inlineStr">
+        <is>
+          <t>Fri, Sep 4, 2026</t>
+        </is>
+      </c>
+      <c r="C1417" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="D1417" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="E1417" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="F1417" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="n">
+        <v>1023042</v>
+      </c>
+      <c r="B1418" t="inlineStr">
+        <is>
+          <t>Fri, Sep 4, 2026</t>
+        </is>
+      </c>
+      <c r="C1418" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="D1418" t="inlineStr">
+        <is>
+          <t>London Knights</t>
+        </is>
+      </c>
+      <c r="E1418" t="inlineStr">
+        <is>
+          <t>London Knights</t>
+        </is>
+      </c>
+      <c r="F1418" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1418"/>
+  <dimension ref="A1:I1428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -46969,8 +46969,13 @@
           <t>Seattle Thunderbirds</t>
         </is>
       </c>
-      <c r="F1409" t="n">
-        <v/>
+      <c r="F1409" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="G1409" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1410">
@@ -46997,8 +47002,13 @@
           <t>Spokane Chiefs</t>
         </is>
       </c>
-      <c r="F1410" t="n">
-        <v/>
+      <c r="F1410" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="G1410" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1411">
@@ -47025,8 +47035,13 @@
           <t>Brandon Wheat Kings</t>
         </is>
       </c>
-      <c r="F1411" t="n">
-        <v/>
+      <c r="F1411" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="G1411" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1412">
@@ -47053,8 +47068,13 @@
           <t>Calgary Hitmen</t>
         </is>
       </c>
-      <c r="F1412" t="n">
-        <v/>
+      <c r="F1412" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="G1412" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1413">
@@ -47081,8 +47101,13 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1413" t="n">
-        <v/>
+      <c r="F1413" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="G1413" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1414">
@@ -47109,8 +47134,13 @@
           <t>Saskatoon Blades</t>
         </is>
       </c>
-      <c r="F1414" t="n">
-        <v/>
+      <c r="F1414" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="G1414" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1415">
@@ -47137,8 +47167,13 @@
           <t>Everett Silvertips</t>
         </is>
       </c>
-      <c r="F1415" t="n">
-        <v/>
+      <c r="F1415" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="G1415" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1416">
@@ -47165,8 +47200,13 @@
           <t>Kelowna Rockets</t>
         </is>
       </c>
-      <c r="F1416" t="n">
-        <v/>
+      <c r="F1416" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="G1416" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1417">
@@ -47193,8 +47233,13 @@
           <t>Edmonton Oil Kings</t>
         </is>
       </c>
-      <c r="F1417" t="n">
-        <v/>
+      <c r="F1417" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="G1417" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1418">
@@ -47221,7 +47266,292 @@
           <t>London Knights</t>
         </is>
       </c>
-      <c r="F1418" t="n">
+      <c r="F1418" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="G1418" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="n">
+        <v>1023050</v>
+      </c>
+      <c r="B1419" t="inlineStr">
+        <is>
+          <t>Sat, Sep 5, 2026</t>
+        </is>
+      </c>
+      <c r="C1419" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="D1419" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="E1419" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="F1419" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="n">
+        <v>1023051</v>
+      </c>
+      <c r="B1420" t="inlineStr">
+        <is>
+          <t>Sat, Sep 5, 2026</t>
+        </is>
+      </c>
+      <c r="C1420" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="D1420" t="inlineStr">
+        <is>
+          <t>London Knights</t>
+        </is>
+      </c>
+      <c r="E1420" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="F1420" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="n">
+        <v>1023047</v>
+      </c>
+      <c r="B1421" t="inlineStr">
+        <is>
+          <t>Sat, Sep 5, 2026</t>
+        </is>
+      </c>
+      <c r="C1421" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="D1421" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="E1421" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="F1421" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="n">
+        <v>1023048</v>
+      </c>
+      <c r="B1422" t="inlineStr">
+        <is>
+          <t>Sat, Sep 5, 2026</t>
+        </is>
+      </c>
+      <c r="C1422" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="D1422" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="E1422" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="F1422" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="n">
+        <v>1023043</v>
+      </c>
+      <c r="B1423" t="inlineStr">
+        <is>
+          <t>Sat, Sep 5, 2026</t>
+        </is>
+      </c>
+      <c r="C1423" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="D1423" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="E1423" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="F1423" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="n">
+        <v>1023045</v>
+      </c>
+      <c r="B1424" t="inlineStr">
+        <is>
+          <t>Sat, Sep 5, 2026</t>
+        </is>
+      </c>
+      <c r="C1424" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="D1424" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="E1424" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="F1424" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="n">
+        <v>1023046</v>
+      </c>
+      <c r="B1425" t="inlineStr">
+        <is>
+          <t>Sat, Sep 5, 2026</t>
+        </is>
+      </c>
+      <c r="C1425" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="D1425" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="E1425" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="F1425" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="n">
+        <v>1023049</v>
+      </c>
+      <c r="B1426" t="inlineStr">
+        <is>
+          <t>Sat, Sep 5, 2026</t>
+        </is>
+      </c>
+      <c r="C1426" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="D1426" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="E1426" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1426" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="n">
+        <v>1023052</v>
+      </c>
+      <c r="B1427" t="inlineStr">
+        <is>
+          <t>Sat, Sep 5, 2026</t>
+        </is>
+      </c>
+      <c r="C1427" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="D1427" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="E1427" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="F1427" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="n">
+        <v>1023044</v>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t>Sat, Sep 5, 2026</t>
+        </is>
+      </c>
+      <c r="C1428" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="D1428" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="E1428" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="F1428" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1428"/>
+  <dimension ref="A1:I1431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -47299,8 +47299,13 @@
           <t>Spokane Chiefs</t>
         </is>
       </c>
-      <c r="F1419" t="n">
-        <v/>
+      <c r="F1419" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="G1419" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1420">
@@ -47327,8 +47332,13 @@
           <t>Victoria Royals</t>
         </is>
       </c>
-      <c r="F1420" t="n">
-        <v/>
+      <c r="F1420" t="inlineStr">
+        <is>
+          <t>London Knights</t>
+        </is>
+      </c>
+      <c r="G1420" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1421">
@@ -47355,8 +47365,13 @@
           <t>Calgary Hitmen</t>
         </is>
       </c>
-      <c r="F1421" t="n">
-        <v/>
+      <c r="F1421" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="G1421" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1422">
@@ -47383,8 +47398,13 @@
           <t>Regina Pats</t>
         </is>
       </c>
-      <c r="F1422" t="n">
-        <v/>
+      <c r="F1422" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="G1422" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1423">
@@ -47411,8 +47431,13 @@
           <t>Everett Silvertips</t>
         </is>
       </c>
-      <c r="F1423" t="n">
-        <v/>
+      <c r="F1423" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="G1423" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1424">
@@ -47439,8 +47464,13 @@
           <t>Medicine Hat Tigers</t>
         </is>
       </c>
-      <c r="F1424" t="n">
-        <v/>
+      <c r="F1424" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="G1424" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1425">
@@ -47467,8 +47497,13 @@
           <t>Swift Current Broncos</t>
         </is>
       </c>
-      <c r="F1425" t="n">
-        <v/>
+      <c r="F1425" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="G1425" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1426">
@@ -47495,8 +47530,13 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1426" t="n">
-        <v/>
+      <c r="F1426" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="G1426" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1427">
@@ -47523,8 +47563,13 @@
           <t>Tri-City Americans</t>
         </is>
       </c>
-      <c r="F1427" t="n">
-        <v/>
+      <c r="F1427" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="G1427" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1428">
@@ -47551,7 +47596,96 @@
           <t>Kamloops Blazers</t>
         </is>
       </c>
-      <c r="F1428" t="n">
+      <c r="F1428" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="G1428" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="n">
+        <v>1023054</v>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>Sun, Sep 6, 2026</t>
+        </is>
+      </c>
+      <c r="C1429" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="D1429" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="E1429" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="F1429" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="n">
+        <v>1023055</v>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t>Sun, Sep 6, 2026</t>
+        </is>
+      </c>
+      <c r="C1430" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="D1430" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="E1430" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="F1430" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="n">
+        <v>1023053</v>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t>Sun, Sep 6, 2026</t>
+        </is>
+      </c>
+      <c r="C1431" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="D1431" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="E1431" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="F1431" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1431"/>
+  <dimension ref="A1:I1433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -47629,8 +47629,13 @@
           <t>Edmonton Oil Kings</t>
         </is>
       </c>
-      <c r="F1429" t="n">
-        <v/>
+      <c r="F1429" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="G1429" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1430">
@@ -47657,8 +47662,13 @@
           <t>Vancouver Giants</t>
         </is>
       </c>
-      <c r="F1430" t="n">
-        <v/>
+      <c r="F1430" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="G1430" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1431">
@@ -47685,7 +47695,68 @@
           <t>Everett Silvertips</t>
         </is>
       </c>
-      <c r="F1431" t="n">
+      <c r="F1431" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="G1431" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="n">
+        <v>1023056</v>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t>Tue, Sep 8, 2026</t>
+        </is>
+      </c>
+      <c r="C1432" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="D1432" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="E1432" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="F1432" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="n">
+        <v>1023057</v>
+      </c>
+      <c r="B1433" t="inlineStr">
+        <is>
+          <t>Tue, Sep 8, 2026</t>
+        </is>
+      </c>
+      <c r="C1433" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="D1433" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="E1433" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="F1433" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1433"/>
+  <dimension ref="A1:I1434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -47728,8 +47728,13 @@
           <t>Regina Pats</t>
         </is>
       </c>
-      <c r="F1432" t="n">
-        <v/>
+      <c r="F1432" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="G1432" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1433">
@@ -47756,7 +47761,40 @@
           <t>Kamloops Blazers</t>
         </is>
       </c>
-      <c r="F1433" t="n">
+      <c r="F1433" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="G1433" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="n">
+        <v>1023058</v>
+      </c>
+      <c r="B1434" t="inlineStr">
+        <is>
+          <t>Wed, Sep 9, 2026</t>
+        </is>
+      </c>
+      <c r="C1434" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="D1434" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="E1434" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="F1434" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1434"/>
+  <dimension ref="A1:I1436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -47794,7 +47794,68 @@
           <t>Penticton Vees</t>
         </is>
       </c>
-      <c r="F1434" t="n">
+      <c r="F1434" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="G1434" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="n">
+        <v>1023059</v>
+      </c>
+      <c r="B1435" t="inlineStr">
+        <is>
+          <t>Thu, Sep 10, 2026</t>
+        </is>
+      </c>
+      <c r="C1435" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="D1435" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="E1435" t="inlineStr">
+        <is>
+          <t>Lethbridge Hurricanes</t>
+        </is>
+      </c>
+      <c r="F1435" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" t="n">
+        <v>1023060</v>
+      </c>
+      <c r="B1436" t="inlineStr">
+        <is>
+          <t>Thu, Sep 10, 2026</t>
+        </is>
+      </c>
+      <c r="C1436" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="D1436" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="E1436" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1436" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1436"/>
+  <dimension ref="A1:I1443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -47827,8 +47827,13 @@
           <t>Lethbridge Hurricanes</t>
         </is>
       </c>
-      <c r="F1435" t="n">
-        <v/>
+      <c r="F1435" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="G1435" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1436">
@@ -47855,7 +47860,208 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1436" t="n">
+      <c r="F1436" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="G1436" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" t="n">
+        <v>1023066</v>
+      </c>
+      <c r="B1437" t="inlineStr">
+        <is>
+          <t>Fri, Sep 11, 2026</t>
+        </is>
+      </c>
+      <c r="C1437" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="D1437" t="inlineStr">
+        <is>
+          <t>Wenatchee Wild</t>
+        </is>
+      </c>
+      <c r="E1437" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="F1437" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="n">
+        <v>1023061</v>
+      </c>
+      <c r="B1438" t="inlineStr">
+        <is>
+          <t>Fri, Sep 11, 2026</t>
+        </is>
+      </c>
+      <c r="C1438" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="D1438" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="E1438" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="F1438" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="n">
+        <v>1023063</v>
+      </c>
+      <c r="B1439" t="inlineStr">
+        <is>
+          <t>Fri, Sep 11, 2026</t>
+        </is>
+      </c>
+      <c r="C1439" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="D1439" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="E1439" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="F1439" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" t="n">
+        <v>1023064</v>
+      </c>
+      <c r="B1440" t="inlineStr">
+        <is>
+          <t>Fri, Sep 11, 2026</t>
+        </is>
+      </c>
+      <c r="C1440" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="D1440" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="E1440" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="F1440" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="n">
+        <v>1023065</v>
+      </c>
+      <c r="B1441" t="inlineStr">
+        <is>
+          <t>Fri, Sep 11, 2026</t>
+        </is>
+      </c>
+      <c r="C1441" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="D1441" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="E1441" t="inlineStr">
+        <is>
+          <t>Prince Albert Raiders</t>
+        </is>
+      </c>
+      <c r="F1441" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="n">
+        <v>1023067</v>
+      </c>
+      <c r="B1442" t="inlineStr">
+        <is>
+          <t>Fri, Sep 11, 2026</t>
+        </is>
+      </c>
+      <c r="C1442" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="D1442" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="E1442" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="F1442" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="n">
+        <v>1023062</v>
+      </c>
+      <c r="B1443" t="inlineStr">
+        <is>
+          <t>Fri, Sep 11, 2026</t>
+        </is>
+      </c>
+      <c r="C1443" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="D1443" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="E1443" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="F1443" t="n">
         <v/>
       </c>
     </row>

--- a/prediction_record.xlsx
+++ b/prediction_record.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1443"/>
+  <dimension ref="A1:I1452"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.28515625" customWidth="1" min="1" max="1"/>
@@ -47893,8 +47893,13 @@
           <t>Seattle Thunderbirds</t>
         </is>
       </c>
-      <c r="F1437" t="n">
-        <v/>
+      <c r="F1437" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="G1437" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1438">
@@ -47921,8 +47926,13 @@
           <t>Brandon Wheat Kings</t>
         </is>
       </c>
-      <c r="F1438" t="n">
-        <v/>
+      <c r="F1438" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="G1438" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1439">
@@ -47949,8 +47959,13 @@
           <t>Medicine Hat Tigers</t>
         </is>
       </c>
-      <c r="F1439" t="n">
-        <v/>
+      <c r="F1439" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="G1439" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1440">
@@ -47977,8 +47992,13 @@
           <t>Edmonton Oil Kings</t>
         </is>
       </c>
-      <c r="F1440" t="n">
-        <v/>
+      <c r="F1440" t="inlineStr">
+        <is>
+          <t>Red Deer Rebels</t>
+        </is>
+      </c>
+      <c r="G1440" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1441">
@@ -48005,8 +48025,13 @@
           <t>Prince Albert Raiders</t>
         </is>
       </c>
-      <c r="F1441" t="n">
-        <v/>
+      <c r="F1441" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="G1441" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="1442">
@@ -48033,8 +48058,13 @@
           <t>Spokane Chiefs</t>
         </is>
       </c>
-      <c r="F1442" t="n">
-        <v/>
+      <c r="F1442" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="G1442" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="1443">
@@ -48061,7 +48091,264 @@
           <t>Everett Silvertips</t>
         </is>
       </c>
-      <c r="F1443" t="n">
+      <c r="F1443" t="inlineStr">
+        <is>
+          <t>Everett Silvertips</t>
+        </is>
+      </c>
+      <c r="G1443" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="n">
+        <v>1023071</v>
+      </c>
+      <c r="B1444" t="inlineStr">
+        <is>
+          <t>Sat, Sep 12, 2026</t>
+        </is>
+      </c>
+      <c r="C1444" t="inlineStr">
+        <is>
+          <t>Portland Winterhawks</t>
+        </is>
+      </c>
+      <c r="D1444" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="E1444" t="inlineStr">
+        <is>
+          <t>Seattle Thunderbirds</t>
+        </is>
+      </c>
+      <c r="F1444" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" t="n">
+        <v>1023074</v>
+      </c>
+      <c r="B1445" t="inlineStr">
+        <is>
+          <t>Sat, Sep 12, 2026</t>
+        </is>
+      </c>
+      <c r="C1445" t="inlineStr">
+        <is>
+          <t>Swift Current Broncos</t>
+        </is>
+      </c>
+      <c r="D1445" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="E1445" t="inlineStr">
+        <is>
+          <t>Medicine Hat Tigers</t>
+        </is>
+      </c>
+      <c r="F1445" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" t="n">
+        <v>1023068</v>
+      </c>
+      <c r="B1446" t="inlineStr">
+        <is>
+          <t>Sat, Sep 12, 2026</t>
+        </is>
+      </c>
+      <c r="C1446" t="inlineStr">
+        <is>
+          <t>Edmonton Oil Kings</t>
+        </is>
+      </c>
+      <c r="D1446" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="E1446" t="inlineStr">
+        <is>
+          <t>Calgary Hitmen</t>
+        </is>
+      </c>
+      <c r="F1446" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" t="n">
+        <v>1023070</v>
+      </c>
+      <c r="B1447" t="inlineStr">
+        <is>
+          <t>Sat, Sep 12, 2026</t>
+        </is>
+      </c>
+      <c r="C1447" t="inlineStr">
+        <is>
+          <t>Moose Jaw Warriors</t>
+        </is>
+      </c>
+      <c r="D1447" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="E1447" t="inlineStr">
+        <is>
+          <t>Brandon Wheat Kings</t>
+        </is>
+      </c>
+      <c r="F1447" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" t="n">
+        <v>1023072</v>
+      </c>
+      <c r="B1448" t="inlineStr">
+        <is>
+          <t>Sat, Sep 12, 2026</t>
+        </is>
+      </c>
+      <c r="C1448" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="D1448" t="inlineStr">
+        <is>
+          <t>Kamloops Blazers</t>
+        </is>
+      </c>
+      <c r="E1448" t="inlineStr">
+        <is>
+          <t>Prince George Cougars</t>
+        </is>
+      </c>
+      <c r="F1448" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" t="n">
+        <v>1023073</v>
+      </c>
+      <c r="B1449" t="inlineStr">
+        <is>
+          <t>Sat, Sep 12, 2026</t>
+        </is>
+      </c>
+      <c r="C1449" t="inlineStr">
+        <is>
+          <t>Saskatoon Blades</t>
+        </is>
+      </c>
+      <c r="D1449" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="E1449" t="inlineStr">
+        <is>
+          <t>Regina Pats</t>
+        </is>
+      </c>
+      <c r="F1449" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" t="n">
+        <v>1023069</v>
+      </c>
+      <c r="B1450" t="inlineStr">
+        <is>
+          <t>Sat, Sep 12, 2026</t>
+        </is>
+      </c>
+      <c r="C1450" t="inlineStr">
+        <is>
+          <t>Kelowna Rockets</t>
+        </is>
+      </c>
+      <c r="D1450" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="E1450" t="inlineStr">
+        <is>
+          <t>Penticton Vees</t>
+        </is>
+      </c>
+      <c r="F1450" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" t="n">
+        <v>1023075</v>
+      </c>
+      <c r="B1451" t="inlineStr">
+        <is>
+          <t>Sat, Sep 12, 2026</t>
+        </is>
+      </c>
+      <c r="C1451" t="inlineStr">
+        <is>
+          <t>Tri-City Americans</t>
+        </is>
+      </c>
+      <c r="D1451" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="E1451" t="inlineStr">
+        <is>
+          <t>Spokane Chiefs</t>
+        </is>
+      </c>
+      <c r="F1451" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" t="n">
+        <v>1023076</v>
+      </c>
+      <c r="B1452" t="inlineStr">
+        <is>
+          <t>Sat, Sep 12, 2026</t>
+        </is>
+      </c>
+      <c r="C1452" t="inlineStr">
+        <is>
+          <t>Vancouver Giants</t>
+        </is>
+      </c>
+      <c r="D1452" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="E1452" t="inlineStr">
+        <is>
+          <t>Victoria Royals</t>
+        </is>
+      </c>
+      <c r="F1452" t="n">
         <v/>
       </c>
     </row>
